--- a/AAII_Financials/Quarterly/GAP_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GAP_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="92">
   <si>
     <t>GAP</t>
   </si>
@@ -656,215 +656,239 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46235</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46144</v>
+      </c>
+      <c r="F7" s="2">
         <v>46053</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45962</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45871</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45780</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45689</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45598</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45507</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45416</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45325</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45227</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>45136</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>45045</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44954</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44863</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>3651000</v>
+      </c>
+      <c r="E8" s="3">
+        <v>3497000</v>
+      </c>
+      <c r="F8" s="3">
         <v>4236000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>3942000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>3725000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>3463000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>4149000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>3829000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>3720000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>3388000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>4298000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>3767000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>3548000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>3276000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>4243000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>4039000</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>2139000</v>
+      </c>
+      <c r="E9" s="3">
+        <v>2080000</v>
+      </c>
+      <c r="F9" s="3">
         <v>2622000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>2272000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>2189000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>2015000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>2537000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>2194000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>2137000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>1991000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>2626000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>2211000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>2215000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>2062000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>2819000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>2530000</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1512000</v>
+      </c>
+      <c r="E10" s="3">
+        <v>1417000</v>
+      </c>
+      <c r="F10" s="3">
         <v>1614000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>1670000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>1536000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>1448000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>1612000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>1635000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>1583000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>1397000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>1672000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>1556000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>1333000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>1214000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>1424000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>1509000</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -882,44 +906,46 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="3">
+      <c r="D12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" s="3">
         <v>60000</v>
       </c>
-      <c r="E12" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="G12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H12" s="3">
+      <c r="H12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J12" s="3">
         <v>40000</v>
       </c>
-      <c r="I12" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="K12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L12" s="3">
+      <c r="L12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N12" s="3">
         <v>37000</v>
       </c>
-      <c r="M12" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N12" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O12" s="3" t="s">
         <v>8</v>
       </c>
@@ -929,8 +955,14 @@
       <c r="Q12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -976,13 +1008,19 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+      <c r="S13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>8</v>
+      <c r="D14" s="3">
+        <v>-417000</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>8</v>
@@ -1005,73 +1043,85 @@
       <c r="K14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L14" s="3">
+      <c r="L14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N14" s="3">
         <v>7000</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P14" s="3">
         <v>13000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="Q14" s="3">
         <v>24000</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>131000</v>
+      </c>
+      <c r="E15" s="3">
         <v>128000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
+        <v>128000</v>
+      </c>
+      <c r="G15" s="3">
         <v>125000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="H15" s="3">
         <v>122000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="I15" s="3">
         <v>121000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="J15" s="3">
         <v>129000</v>
-      </c>
-      <c r="I15" s="3">
-        <v>124000</v>
-      </c>
-      <c r="J15" s="3">
-        <v>123000</v>
       </c>
       <c r="K15" s="3">
         <v>124000</v>
       </c>
       <c r="L15" s="3">
+        <v>123000</v>
+      </c>
+      <c r="M15" s="3">
+        <v>124000</v>
+      </c>
+      <c r="N15" s="3">
         <v>128000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="O15" s="3">
         <v>127000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="P15" s="3">
         <v>130000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="Q15" s="3">
         <v>137000</v>
       </c>
-      <c r="P15" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R15" s="3">
+        <v>0</v>
+      </c>
+      <c r="S15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1086,102 +1136,116 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>3406000</v>
+      </c>
+      <c r="E17" s="3">
+        <v>3052000</v>
+      </c>
+      <c r="F17" s="3">
         <v>4029000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>3618000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>3434000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>3203000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>3871000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>3478000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>3433000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>3183000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>4054000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>3544000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>3419000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>3262000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>4273000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>3853000</v>
       </c>
     </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>245000</v>
+      </c>
+      <c r="E18" s="3">
+        <v>445000</v>
+      </c>
+      <c r="F18" s="3">
         <v>207000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>324000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>291000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>260000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>278000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>351000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>287000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>205000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>244000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>223000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>129000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>14000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>-30000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>186000</v>
       </c>
     </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1199,102 +1263,116 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-14000</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F20" s="3">
         <v>-22000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>-10000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>-1000</v>
       </c>
-      <c r="G20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J20" s="3">
         <v>19000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>-4000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>-6000</v>
       </c>
-      <c r="K20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N20" s="3">
         <v>23000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>-27000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>10000</v>
       </c>
-      <c r="O20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R20" s="3">
         <v>12000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>4000</v>
       </c>
     </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>390000</v>
+      </c>
+      <c r="E21" s="3">
+        <v>573000</v>
+      </c>
+      <c r="F21" s="3">
         <v>357000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>459000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>414000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>381000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>388000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>479000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>416000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>329000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>349000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>377000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>249000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>151000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>120000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>330000</v>
       </c>
     </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1302,140 +1380,158 @@
         <v>24000</v>
       </c>
       <c r="E22" s="3">
-        <v>23000</v>
+        <v>22000</v>
       </c>
       <c r="F22" s="3">
-        <v>23000</v>
+        <v>24000</v>
       </c>
       <c r="G22" s="3">
         <v>23000</v>
       </c>
       <c r="H22" s="3">
-        <v>19000</v>
+        <v>23000</v>
       </c>
       <c r="I22" s="3">
         <v>23000</v>
       </c>
       <c r="J22" s="3">
-        <v>24000</v>
+        <v>19000</v>
       </c>
       <c r="K22" s="3">
-        <v>21000</v>
+        <v>23000</v>
       </c>
       <c r="L22" s="3">
         <v>24000</v>
       </c>
       <c r="M22" s="3">
+        <v>21000</v>
+      </c>
+      <c r="N22" s="3">
+        <v>24000</v>
+      </c>
+      <c r="O22" s="3">
         <v>28000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="P22" s="3">
         <v>15000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="Q22" s="3">
         <v>23000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="R22" s="3">
         <v>25000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="S22" s="3">
         <v>22000</v>
       </c>
     </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>680000</v>
+      </c>
+      <c r="E23" s="3">
+        <v>450000</v>
+      </c>
+      <c r="F23" s="3">
         <v>236000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>337000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>296000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>263000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>272000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>361000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>296000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>208000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>218000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>250000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>108000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-20000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-43000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>168000</v>
       </c>
     </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>179000</v>
+      </c>
+      <c r="E24" s="3">
+        <v>111000</v>
+      </c>
+      <c r="F24" s="3">
         <v>65000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>101000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>80000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>70000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>66000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>87000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>90000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>50000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>33000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>32000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>-9000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>-2000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>230000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>-114000</v>
       </c>
     </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1481,102 +1577,120 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+      <c r="S25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>501000</v>
+      </c>
+      <c r="E26" s="3">
+        <v>339000</v>
+      </c>
+      <c r="F26" s="3">
         <v>171000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>236000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>216000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>193000</v>
-      </c>
-      <c r="H26" s="3">
-        <v>206000</v>
-      </c>
-      <c r="I26" s="3">
-        <v>274000</v>
       </c>
       <c r="J26" s="3">
         <v>206000</v>
       </c>
       <c r="K26" s="3">
+        <v>274000</v>
+      </c>
+      <c r="L26" s="3">
+        <v>206000</v>
+      </c>
+      <c r="M26" s="3">
         <v>158000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>185000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>218000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>117000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-18000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-273000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>282000</v>
       </c>
     </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>501000</v>
+      </c>
+      <c r="E27" s="3">
+        <v>339000</v>
+      </c>
+      <c r="F27" s="3">
         <v>171000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>236000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>216000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>193000</v>
-      </c>
-      <c r="H27" s="3">
-        <v>206000</v>
-      </c>
-      <c r="I27" s="3">
-        <v>274000</v>
       </c>
       <c r="J27" s="3">
         <v>206000</v>
       </c>
       <c r="K27" s="3">
+        <v>274000</v>
+      </c>
+      <c r="L27" s="3">
+        <v>206000</v>
+      </c>
+      <c r="M27" s="3">
         <v>158000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>185000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>218000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>117000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-18000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-273000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>282000</v>
       </c>
     </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1622,8 +1736,14 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+      <c r="S28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1669,8 +1789,14 @@
       <c r="Q29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+      <c r="S29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1716,8 +1842,14 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+      <c r="S30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1763,102 +1895,120 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+      <c r="S31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>14000</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F32" s="3">
         <v>22000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>10000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>1000</v>
       </c>
-      <c r="G32" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J32" s="3">
         <v>-19000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>4000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>6000</v>
       </c>
-      <c r="K32" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N32" s="3">
         <v>-23000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>27000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>-10000</v>
       </c>
-      <c r="O32" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R32" s="3">
         <v>-12000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>-4000</v>
       </c>
     </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>501000</v>
+      </c>
+      <c r="E33" s="3">
+        <v>339000</v>
+      </c>
+      <c r="F33" s="3">
         <v>171000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>236000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>216000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>193000</v>
-      </c>
-      <c r="H33" s="3">
-        <v>206000</v>
-      </c>
-      <c r="I33" s="3">
-        <v>274000</v>
       </c>
       <c r="J33" s="3">
         <v>206000</v>
       </c>
       <c r="K33" s="3">
+        <v>274000</v>
+      </c>
+      <c r="L33" s="3">
+        <v>206000</v>
+      </c>
+      <c r="M33" s="3">
         <v>158000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>185000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>218000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>117000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-18000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-273000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>282000</v>
       </c>
     </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1904,107 +2054,125 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+      <c r="S34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>501000</v>
+      </c>
+      <c r="E35" s="3">
+        <v>339000</v>
+      </c>
+      <c r="F35" s="3">
         <v>171000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>236000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>216000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>193000</v>
-      </c>
-      <c r="H35" s="3">
-        <v>206000</v>
-      </c>
-      <c r="I35" s="3">
-        <v>274000</v>
       </c>
       <c r="J35" s="3">
         <v>206000</v>
       </c>
       <c r="K35" s="3">
+        <v>274000</v>
+      </c>
+      <c r="L35" s="3">
+        <v>206000</v>
+      </c>
+      <c r="M35" s="3">
         <v>158000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>185000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>218000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>117000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-18000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-273000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>282000</v>
       </c>
     </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46235</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46144</v>
+      </c>
+      <c r="F38" s="2">
         <v>46053</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45962</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45871</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45780</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45689</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45598</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45507</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45416</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45325</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45227</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>45136</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>45045</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44954</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44863</v>
       </c>
     </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2022,8 +2190,10 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2041,290 +2211,328 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2103000</v>
+      </c>
+      <c r="E41" s="3">
+        <v>2162000</v>
+      </c>
+      <c r="F41" s="3">
         <v>2616000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>2262000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>2194000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>1976000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>2335000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>1969000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>1900000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>1532000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>1873000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>1351000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>1350000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>1170000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>1215000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>679000</v>
       </c>
     </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>382000</v>
+      </c>
+      <c r="E42" s="3">
+        <v>399000</v>
+      </c>
+      <c r="F42" s="3">
         <v>386000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>255000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>238000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>244000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>253000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>250000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>246000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>199000</v>
       </c>
-      <c r="L42" s="3">
-        <v>0</v>
-      </c>
-      <c r="M42" s="3">
-        <v>0</v>
-      </c>
       <c r="N42" s="3">
         <v>0</v>
       </c>
       <c r="O42" s="3">
         <v>0</v>
       </c>
-      <c r="P42" s="3" t="s">
-        <v>8</v>
+      <c r="P42" s="3">
+        <v>0</v>
       </c>
       <c r="Q42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R42" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3">
+      <c r="D43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F43" s="3">
         <v>316000</v>
       </c>
-      <c r="E43" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F43" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="G43" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H43" s="3">
+      <c r="H43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J43" s="3">
         <v>301000</v>
       </c>
-      <c r="I43" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J43" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="K43" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L43" s="3">
+      <c r="L43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N43" s="3">
         <v>289000</v>
       </c>
-      <c r="M43" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N43" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O43" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P43" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q43" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="P43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R43" s="3">
+        <v>0</v>
+      </c>
+      <c r="S43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>2297000</v>
+      </c>
+      <c r="E44" s="3">
+        <v>2095000</v>
+      </c>
+      <c r="F44" s="3">
         <v>2207000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>2459000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>2294000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>2097000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>2067000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>2331000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>2107000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>1952000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>1995000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>2377000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>2226000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>2299000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>2389000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>3043000</v>
       </c>
     </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1088000</v>
+      </c>
+      <c r="E45" s="3">
+        <v>583000</v>
+      </c>
+      <c r="F45" s="3">
         <v>252000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>664000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>651000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>567000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>247000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>580000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>556000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>514000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>207000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>646000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>663000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>814000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>1013000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>1316000</v>
       </c>
     </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>5870000</v>
+      </c>
+      <c r="E46" s="3">
+        <v>5239000</v>
+      </c>
+      <c r="F46" s="3">
         <v>5777000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>5640000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>5377000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>4884000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>5203000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>5130000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>4809000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>4197000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>4395000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>4374000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>4239000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>4283000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>4617000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>5038000</v>
       </c>
     </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2364,97 +2572,109 @@
       <c r="O47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P47" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q47" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="P47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R47" s="3">
+        <v>0</v>
+      </c>
+      <c r="S47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>6112000</v>
+      </c>
+      <c r="E48" s="3">
+        <v>6015000</v>
+      </c>
+      <c r="F48" s="3">
         <v>5950000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>5854000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>5875000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>5737000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>5736000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>5763000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>5710000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>5735000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>5681000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>5752000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>5708000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>5769000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>5861000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>6129000</v>
       </c>
     </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>0</v>
+      </c>
+      <c r="E49" s="3">
+        <v>0</v>
+      </c>
+      <c r="F49" s="3">
         <v>270000</v>
       </c>
-      <c r="E49" s="3">
-        <v>0</v>
-      </c>
-      <c r="F49" s="3">
-        <v>0</v>
-      </c>
       <c r="G49" s="3">
         <v>0</v>
       </c>
       <c r="H49" s="3">
+        <v>0</v>
+      </c>
+      <c r="I49" s="3">
+        <v>0</v>
+      </c>
+      <c r="J49" s="3">
         <v>276000</v>
       </c>
-      <c r="I49" s="3">
-        <v>0</v>
-      </c>
-      <c r="J49" s="3">
-        <v>0</v>
-      </c>
       <c r="K49" s="3">
         <v>0</v>
       </c>
       <c r="L49" s="3">
+        <v>0</v>
+      </c>
+      <c r="M49" s="3">
+        <v>0</v>
+      </c>
+      <c r="N49" s="3">
         <v>279000</v>
       </c>
-      <c r="M49" s="3">
-        <v>0</v>
-      </c>
-      <c r="N49" s="3">
-        <v>0</v>
-      </c>
       <c r="O49" s="3">
         <v>0</v>
       </c>
@@ -2464,8 +2684,14 @@
       <c r="Q49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R49" s="3">
+        <v>0</v>
+      </c>
+      <c r="S49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2511,8 +2737,14 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+      <c r="S50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2558,55 +2790,67 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+      <c r="S51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>874000</v>
+      </c>
+      <c r="E52" s="3">
+        <v>883000</v>
+      </c>
+      <c r="F52" s="3">
         <v>635000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>876000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>894000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>944000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>670000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>960000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>990000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>976000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>689000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>926000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>903000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>880000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>908000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>833000</v>
       </c>
     </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2652,55 +2896,67 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+      <c r="S53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>12856000</v>
+      </c>
+      <c r="E54" s="3">
+        <v>12137000</v>
+      </c>
+      <c r="F54" s="3">
         <v>12632000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>12370000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>12146000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>11565000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>11885000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>11853000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>11509000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>10908000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>11044000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>11052000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>10850000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>10932000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>11386000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>12000000</v>
       </c>
     </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2718,8 +2974,10 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2737,290 +2995,328 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1696000</v>
+      </c>
+      <c r="E57" s="3">
+        <v>1298000</v>
+      </c>
+      <c r="F57" s="3">
         <v>1567000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>1545000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>1656000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>1292000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>1488000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>1523000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>1522000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>1196000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>1349000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>1433000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>1406000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>1199000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>1320000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>1388000</v>
       </c>
     </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>618000</v>
+      </c>
+      <c r="E58" s="3">
+        <v>631000</v>
+      </c>
+      <c r="F58" s="3">
         <v>634000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>629000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>631000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>633000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>632000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>617000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>613000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>624000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>600000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>604000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>578000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>658000</v>
       </c>
-      <c r="P58" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q58" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R58" s="3">
+        <v>0</v>
+      </c>
+      <c r="S58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>40000</v>
+      </c>
+      <c r="E59" s="3">
+        <v>94000</v>
+      </c>
+      <c r="F59" s="3">
         <v>667000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>38000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>35000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>102000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>618000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>51000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>62000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>44000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>713000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>32000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>50000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>79000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>1936000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>1993000</v>
       </c>
     </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>3221000</v>
+      </c>
+      <c r="E60" s="3">
+        <v>2901000</v>
+      </c>
+      <c r="F60" s="3">
         <v>3300000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>3279000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>3197000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>2854000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>3256000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>3325000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>3224000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>2806000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>3096000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>3139000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>3007000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>2918000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>3256000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>3381000</v>
       </c>
     </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>5102000</v>
+      </c>
+      <c r="E61" s="3">
+        <v>5011000</v>
+      </c>
+      <c r="F61" s="3">
         <v>4977000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>4887000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>4961000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>4853000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>4843000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>4849000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>4846000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>4876000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>4841000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>4944000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>5070000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>5290000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>1836000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>1836000</v>
       </c>
     </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>582000</v>
+      </c>
+      <c r="E62" s="3">
+        <v>570000</v>
+      </c>
+      <c r="F62" s="3">
         <v>554000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>557000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>555000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>537000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>522000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>544000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>538000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>519000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>512000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>509000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>510000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>539000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>4061000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>4212000</v>
       </c>
     </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3066,8 +3362,14 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+      <c r="S63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3113,8 +3415,14 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+      <c r="S64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3160,55 +3468,67 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+      <c r="S65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>8905000</v>
+      </c>
+      <c r="E66" s="3">
+        <v>8482000</v>
+      </c>
+      <c r="F66" s="3">
         <v>8831000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>8723000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>8713000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>8244000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>8621000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>8718000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>8608000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>8201000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>8449000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>8592000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>8587000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>8747000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>9153000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>9429000</v>
       </c>
     </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3226,8 +3546,10 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3273,8 +3595,14 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+      <c r="S68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3320,8 +3648,14 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+      <c r="S69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3367,8 +3701,14 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3414,55 +3754,67 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+      <c r="S71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>3888000</v>
+      </c>
+      <c r="E72" s="3">
+        <v>3602000</v>
+      </c>
+      <c r="F72" s="3">
         <v>3608000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>3499000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>3325000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>3171000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>3039000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>2889000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>2672000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>2522000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>2420000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>2291000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>2128000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>2067000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>2140000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>2468000</v>
       </c>
     </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3508,8 +3860,14 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+      <c r="S73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3555,8 +3913,14 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+      <c r="S74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3602,55 +3966,67 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+      <c r="S75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>3951000</v>
+      </c>
+      <c r="E76" s="3">
+        <v>3655000</v>
+      </c>
+      <c r="F76" s="3">
         <v>3801000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>3647000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>3433000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>3321000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>3264000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>3135000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>2901000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>2707000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>2595000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>2460000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>2263000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>2185000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>2233000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>2571000</v>
       </c>
     </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3696,107 +4072,125 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+      <c r="S77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46235</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46144</v>
+      </c>
+      <c r="F80" s="2">
         <v>46053</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45962</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45871</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45780</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45689</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45598</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45507</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45416</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45325</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45227</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>45136</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>45045</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44954</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44863</v>
       </c>
     </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>501000</v>
+      </c>
+      <c r="E81" s="3">
+        <v>339000</v>
+      </c>
+      <c r="F81" s="3">
         <v>171000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>236000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>216000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>193000</v>
-      </c>
-      <c r="H81" s="3">
-        <v>206000</v>
-      </c>
-      <c r="I81" s="3">
-        <v>274000</v>
       </c>
       <c r="J81" s="3">
         <v>206000</v>
       </c>
       <c r="K81" s="3">
+        <v>274000</v>
+      </c>
+      <c r="L81" s="3">
+        <v>206000</v>
+      </c>
+      <c r="M81" s="3">
         <v>158000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>185000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>218000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>117000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-18000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-273000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>282000</v>
       </c>
     </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3814,55 +4208,63 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>122000</v>
+      </c>
+      <c r="E83" s="3">
         <v>121000</v>
       </c>
-      <c r="E83" s="3">
-        <v>124000</v>
-      </c>
       <c r="F83" s="3">
-        <v>123000</v>
+        <v>121000</v>
       </c>
       <c r="G83" s="3">
         <v>124000</v>
       </c>
       <c r="H83" s="3">
+        <v>123000</v>
+      </c>
+      <c r="I83" s="3">
+        <v>124000</v>
+      </c>
+      <c r="J83" s="3">
         <v>119000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>127000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>130000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>137000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>138000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>140000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>132000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>130000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>138000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="S83" s="3">
         <v>140000</v>
       </c>
     </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3908,8 +4310,14 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+      <c r="S84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3955,8 +4363,14 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+      <c r="S85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4002,8 +4416,14 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+      <c r="S86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4049,8 +4469,14 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+      <c r="S87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4096,55 +4522,67 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+      <c r="S88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>337000</v>
+      </c>
+      <c r="E89" s="3">
+        <v>213000</v>
+      </c>
+      <c r="F89" s="3">
         <v>686000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>299000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>448000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-140000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>616000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>291000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>549000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>30000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>700000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>304000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>513000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>15000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>719000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>95000</v>
       </c>
     </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4162,55 +4600,63 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-154000</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-135000</v>
+      </c>
+      <c r="F91" s="3">
         <v>-143000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-146000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-98000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-83000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-117000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-148000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-89000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-93000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-132000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-89000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-82000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-117000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-108000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-171000</v>
       </c>
     </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4256,8 +4702,14 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+      <c r="S92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4303,55 +4755,67 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+      <c r="S93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-136000</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-149000</v>
+      </c>
+      <c r="F94" s="3">
         <v>-273000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-163000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-91000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-73000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-116000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-151000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-134000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-291000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-131000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-91000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-82000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-30000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-108000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-46000</v>
       </c>
     </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4369,8 +4833,10 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4378,31 +4844,31 @@
         <v>62000</v>
       </c>
       <c r="E96" s="3">
-        <v>62000</v>
+        <v>63000</v>
       </c>
       <c r="F96" s="3">
         <v>62000</v>
       </c>
       <c r="G96" s="3">
+        <v>62000</v>
+      </c>
+      <c r="H96" s="3">
+        <v>62000</v>
+      </c>
+      <c r="I96" s="3">
         <v>61000</v>
-      </c>
-      <c r="H96" s="3">
-        <v>56000</v>
-      </c>
-      <c r="I96" s="3">
-        <v>57000</v>
       </c>
       <c r="J96" s="3">
         <v>56000</v>
       </c>
       <c r="K96" s="3">
-        <v>56000</v>
+        <v>57000</v>
       </c>
       <c r="L96" s="3">
         <v>56000</v>
       </c>
       <c r="M96" s="3">
-        <v>55000</v>
+        <v>56000</v>
       </c>
       <c r="N96" s="3">
         <v>56000</v>
@@ -4411,13 +4877,19 @@
         <v>55000</v>
       </c>
       <c r="P96" s="3">
+        <v>56000</v>
+      </c>
+      <c r="Q96" s="3">
+        <v>55000</v>
+      </c>
+      <c r="R96" s="3">
         <v>-54000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="S96" s="3">
         <v>-55000</v>
       </c>
     </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4463,8 +4935,14 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+      <c r="S97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4510,8 +4988,14 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+      <c r="S98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4557,145 +5041,169 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+      <c r="S99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-258000</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-519000</v>
+      </c>
+      <c r="F100" s="3">
         <v>-61000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-66000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-139000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-153000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-128000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-69000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-47000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-77000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-51000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-207000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-251000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-58000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-54000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>-62000</v>
       </c>
     </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>0</v>
+      </c>
+      <c r="E101" s="3">
+        <v>5000</v>
+      </c>
+      <c r="F101" s="3">
         <v>-5000</v>
-      </c>
-      <c r="E101" s="3">
-        <v>-2000</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
       </c>
       <c r="G101" s="3">
         <v>-2000</v>
       </c>
       <c r="H101" s="3">
+        <v>0</v>
+      </c>
+      <c r="I101" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="J101" s="3">
         <v>4000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>-5000</v>
       </c>
-      <c r="J101" s="3">
-        <v>0</v>
-      </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
+        <v>0</v>
+      </c>
+      <c r="M101" s="3">
         <v>-2000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>10000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>-16000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>-2000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>-7000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="R101" s="3">
         <v>10000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="S101" s="3">
         <v>-16000</v>
       </c>
     </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-59000</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-455000</v>
+      </c>
+      <c r="F102" s="3">
         <v>354000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>68000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>218000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-361000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>367000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>69000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>368000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-340000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>522000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>1000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>180000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-75000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>567000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>-29000</v>
       </c>
     </row>
